--- a/Delta Downs/Doug's Picks/DED_Picks.xlsx
+++ b/Delta Downs/Doug's Picks/DED_Picks.xlsx
@@ -4,11 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25200" windowHeight="11750" activeTab="1"/>
+    <workbookView windowHeight="17600" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="DED 10.21.26" sheetId="1" r:id="rId1"/>
     <sheet name="DED 10.22.26" sheetId="2" r:id="rId2"/>
+    <sheet name="DED10.23.26" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
   <si>
     <t>Race</t>
   </si>
@@ -70,6 +71,18 @@
   </si>
   <si>
     <t>R8</t>
+  </si>
+  <si>
+    <t>P</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>R9</t>
   </si>
 </sst>
 </file>
@@ -1561,4 +1574,193 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="5.45454545454545" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.8181818181818" customWidth="1"/>
+    <col min="4" max="4" width="10.4545454545455" customWidth="1"/>
+    <col min="5" max="5" width="10.3636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>9</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>8</v>
+      </c>
+      <c r="D10">
+        <v>5</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Delta Downs/Doug's Picks/DED_Picks.xlsx
+++ b/Delta Downs/Doug's Picks/DED_Picks.xlsx
@@ -4,12 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17600" activeTab="2"/>
+    <workbookView windowWidth="25200" windowHeight="11750" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="DED 10.21.26" sheetId="1" r:id="rId1"/>
     <sheet name="DED 10.22.26" sheetId="2" r:id="rId2"/>
     <sheet name="DED10.23.26" sheetId="3" r:id="rId3"/>
+    <sheet name="DED 10.24.26" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="18">
   <si>
     <t>Race</t>
   </si>
@@ -1763,4 +1764,193 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="5.45454545454545" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.8181818181818" customWidth="1"/>
+    <col min="4" max="4" width="10.4545454545455" customWidth="1"/>
+    <col min="5" max="5" width="10.3636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>6</v>
+      </c>
+      <c r="E4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>4</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>10</v>
+      </c>
+      <c r="E5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <v>9</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>10</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+      <c r="E7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>10</v>
+      </c>
+      <c r="E8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Delta Downs/Doug's Picks/DED_Picks.xlsx
+++ b/Delta Downs/Doug's Picks/DED_Picks.xlsx
@@ -4,13 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25200" windowHeight="11750" activeTab="3"/>
+    <workbookView windowWidth="25200" windowHeight="11750" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="DED 10.21.26" sheetId="1" r:id="rId1"/>
     <sheet name="DED 10.22.26" sheetId="2" r:id="rId2"/>
     <sheet name="DED10.23.26" sheetId="3" r:id="rId3"/>
     <sheet name="DED 10.24.26" sheetId="4" r:id="rId4"/>
+    <sheet name="DED 10.28.26" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -30,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="18">
   <si>
     <t>Race</t>
   </si>
@@ -1953,4 +1954,176 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="5.45454545454545" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.8181818181818" customWidth="1"/>
+    <col min="4" max="4" width="10.4545454545455" customWidth="1"/>
+    <col min="5" max="5" width="10.3636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+      <c r="E3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+      <c r="E4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+      <c r="C5">
+        <v>6</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+      <c r="C6">
+        <v>7</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>8</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>6</v>
+      </c>
+      <c r="E9">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Delta Downs/Doug's Picks/DED_Picks.xlsx
+++ b/Delta Downs/Doug's Picks/DED_Picks.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25200" windowHeight="11750" activeTab="4"/>
+    <workbookView windowWidth="25200" windowHeight="11750" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="DED 10.21.26" sheetId="1" r:id="rId1"/>
@@ -12,6 +12,7 @@
     <sheet name="DED10.23.26" sheetId="3" r:id="rId3"/>
     <sheet name="DED 10.24.26" sheetId="4" r:id="rId4"/>
     <sheet name="DED 10.28.26" sheetId="5" r:id="rId5"/>
+    <sheet name="DED 10.29.26" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -31,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="18">
   <si>
     <t>Race</t>
   </si>
@@ -2126,4 +2127,169 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E9"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>10</v>
+      </c>
+      <c r="C2">
+        <v>7</v>
+      </c>
+      <c r="D2">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>8</v>
+      </c>
+      <c r="C3">
+        <v>3</v>
+      </c>
+      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>8</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+      <c r="E5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>7</v>
+      </c>
+      <c r="C6">
+        <v>3</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8">
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>
--- a/Delta Downs/Doug's Picks/DED_Picks.xlsx
+++ b/Delta Downs/Doug's Picks/DED_Picks.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25200" windowHeight="11750" activeTab="5"/>
+    <workbookView windowWidth="25200" windowHeight="11750" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="DED 10.21.26" sheetId="1" r:id="rId1"/>
@@ -13,6 +13,7 @@
     <sheet name="DED 10.24.26" sheetId="4" r:id="rId4"/>
     <sheet name="DED 10.28.26" sheetId="5" r:id="rId5"/>
     <sheet name="DED 10.29.26" sheetId="6" r:id="rId6"/>
+    <sheet name="DED 10.30.26" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="18">
   <si>
     <t>Race</t>
   </si>
@@ -2292,4 +2293,193 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E10"/>
+  <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="14.5" outlineLevelCol="4"/>
+  <cols>
+    <col min="1" max="1" width="5.45454545454545" customWidth="1"/>
+    <col min="2" max="2" width="10" customWidth="1"/>
+    <col min="3" max="3" width="10.8181818181818" customWidth="1"/>
+    <col min="4" max="4" width="10.4545454545455" customWidth="1"/>
+    <col min="5" max="5" width="10.3636363636364" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2">
+        <v>9</v>
+      </c>
+      <c r="C2">
+        <v>6</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3">
+        <v>10</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>9</v>
+      </c>
+      <c r="E3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+      <c r="C4">
+        <v>6</v>
+      </c>
+      <c r="D4">
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8">
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9">
+        <v>5</v>
+      </c>
+      <c r="C9">
+        <v>9</v>
+      </c>
+      <c r="D9">
+        <v>10</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10">
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>